--- a/reddit_tracker/Reddit_Interaction_Tracker.xlsx
+++ b/reddit_tracker/Reddit_Interaction_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\reddit_tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CCDF69-488A-4E91-A739-A98A8B8CDC95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B2E9C6B-D931-436B-A97B-04C22F671AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="142">
   <si>
     <t>貼文編號</t>
   </si>
@@ -85,9 +85,6 @@
     <t>2025-10-22</t>
   </si>
   <si>
-    <t>22:00</t>
-  </si>
-  <si>
     <t>r/PhiladelphiaEats</t>
   </si>
   <si>
@@ -452,13 +449,17 @@
   </si>
   <si>
     <t>待收集</t>
+  </si>
+  <si>
+    <t>https://www.reddit.com/r/PhiladelphiaEats/comments/1odq36w/favorite_wine_shops_in_philly_with_friendly_staff/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +479,14 @@
       <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -513,17 +522,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -826,6 +840,7 @@
   <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -886,151 +901,154 @@
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="2">
+        <v>45953</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
         <v>23</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
       <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="s">
         <v>23</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>35</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
         <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{6AF62685-F282-4E30-96AA-69141B4953C6}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1042,40 +1060,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -1083,22 +1101,22 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
       </c>
       <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s">
         <v>51</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>52</v>
-      </c>
-      <c r="G2" t="s">
-        <v>53</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -1110,33 +1128,33 @@
         <v>7</v>
       </c>
       <c r="K2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" t="s">
         <v>54</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
         <v>56</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>57</v>
-      </c>
-      <c r="G3" t="s">
-        <v>58</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -1148,10 +1166,10 @@
         <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1167,116 +1185,116 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" t="s">
         <v>71</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>72</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
         <v>73</v>
       </c>
-      <c r="F2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>74</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>75</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>76</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>77</v>
       </c>
-      <c r="K2" t="s">
-        <v>78</v>
-      </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" t="s">
         <v>71</v>
       </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
       <c r="E3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" t="s">
         <v>80</v>
       </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" t="s">
         <v>81</v>
       </c>
-      <c r="I3" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>82</v>
       </c>
-      <c r="K3" t="s">
-        <v>83</v>
-      </c>
       <c r="L3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1292,40 +1310,40 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>15</v>
@@ -1333,84 +1351,84 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
         <v>94</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" t="s">
         <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" t="s">
-        <v>76</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K2" t="s">
         <v>97</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" t="s">
         <v>98</v>
-      </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
         <v>95</v>
       </c>
-      <c r="D3" t="s">
-        <v>96</v>
-      </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1426,31 +1444,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1473,18 +1491,18 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" t="s">
         <v>109</v>
-      </c>
-      <c r="H2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1502,13 +1520,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1524,45 +1542,45 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -1574,16 +1592,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I2" t="s">
         <v>123</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>124</v>
-      </c>
-      <c r="J2" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1599,33 +1617,33 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1634,44 +1652,44 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" t="s">
         <v>133</v>
-      </c>
-      <c r="G2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" t="s">
         <v>135</v>
       </c>
-      <c r="B3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" t="s">
         <v>136</v>
-      </c>
-      <c r="D3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1680,21 +1698,21 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" t="s">
         <v>139</v>
-      </c>
-      <c r="B5" t="s">
-        <v>140</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -1703,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
